--- a/src/attributions/attributions_ig_traj_165.xlsx
+++ b/src/attributions/attributions_ig_traj_165.xlsx
@@ -999,7 +999,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.09696376164605838</v>
+        <v>0.06124600083791076</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1008,25 +1008,25 @@
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1018093248313472</v>
+        <v>-0.1189651748138245</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03138489194483073</v>
+        <v>-0.01424601952953994</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1192901588442964</v>
+        <v>0.021782835242178</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1035,25 +1035,25 @@
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02281635491791918</v>
+        <v>-0.1456298604466723</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00356015654282134</v>
+        <v>-0.04187935415059184</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01631646556738234</v>
+        <v>-0.01949278228866197</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -1062,91 +1062,91 @@
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0861703985219313</v>
+        <v>-0.01746391317628851</v>
       </c>
       <c r="W2" t="n">
-        <v>0.08507851938581537</v>
+        <v>-0.02805801203167956</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.09083677247884137</v>
+        <v>-0.0184573398462476</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.04702292377022881</v>
+        <v>0.07624185578955998</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.05702354526753739</v>
+        <v>0.1094890607470865</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.01997041041379946</v>
+        <v>0.007254350720616253</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.01607519425480676</v>
+        <v>-0.1055696255151703</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.08149646890013712</v>
+        <v>0.03985162727304909</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
         <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1336501707024003</v>
+        <v>-0.07806069749896738</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.06852541173938405</v>
+        <v>-0.2780201476794619</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2165568478402687</v>
+        <v>-0.1214630870390889</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
@@ -1161,7 +1161,7 @@
         <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.2086055293652667</v>
+        <v>0.1868663047474079</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
@@ -1170,160 +1170,160 @@
         <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.01015945217610379</v>
+        <v>0.1764114157120844</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.002530386602074397</v>
+        <v>0.1570993496109638</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.06762686497363894</v>
+        <v>0.01618903064998393</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.04018246215429826</v>
+        <v>0.009640854409168328</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1738462337235198</v>
+        <v>-0.1120674278706514</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.02802823565795132</v>
+        <v>-0.03558265263180885</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01855011127302498</v>
+        <v>-0.1609763969718964</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.07089959336097378</v>
+        <v>-0.02659587306327436</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.02484109227486015</v>
+        <v>-0.05347552501963583</v>
       </c>
       <c r="CE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.01320057681748943</v>
+        <v>0.1159581423430823</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.01163354871592714</v>
+        <v>0.007617417799483217</v>
       </c>
       <c r="CI2" t="n">
         <v>0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.01328620006436192</v>
+        <v>-0.005324036781995093</v>
       </c>
       <c r="CN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.04770529199714677</v>
+        <v>0.04873039066837605</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.01745211909221465</v>
+        <v>-0.01511442955685638</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.008432849764699447</v>
+        <v>-0.04378268930314346</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX2" t="n">
         <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.02377611483697461</v>
+        <v>0.1186128253392971</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.003771474524692389</v>
+        <v>0.02195533172979081</v>
       </c>
       <c r="DA2" t="n">
         <v>-0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0.01013703470901887</v>
+        <v>-0.01079568702540262</v>
       </c>
       <c r="DF2" t="n">
         <v>-0</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1392698680417173</v>
+        <v>0.08410564577019336</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.08132485963948249</v>
+        <v>-0.02018157757231279</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0.04891804429027107</v>
+        <v>-0.08406286581462527</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.00939598645368892</v>
+        <v>-0.008620172346987953</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.102308345957376</v>
+        <v>0.03050392774638922</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.03403592663511997</v>
+        <v>0.04728221917408083</v>
       </c>
       <c r="DX2" t="n">
         <v>-0</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.06881195975455824</v>
+        <v>0.06928992072351889</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.08257618614409382</v>
+        <v>0.04678198365284444</v>
       </c>
       <c r="EB2" t="n">
         <v>0</v>
@@ -1398,55 +1398,55 @@
         <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.02412693603694778</v>
+        <v>-0.09304627997350247</v>
       </c>
       <c r="EG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.02868384819026934</v>
+        <v>0.08734088790029378</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.05083255077264257</v>
+        <v>0.06033725312884747</v>
       </c>
       <c r="EK2" t="n">
         <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0.01579846651987643</v>
+        <v>0.01852158962657209</v>
       </c>
       <c r="EP2" t="n">
         <v>0</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.03227605526471701</v>
+        <v>0.1124640739688451</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.04026555458870443</v>
+        <v>0.008833848212675532</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
@@ -1458,34 +1458,34 @@
         <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0.007347774351484287</v>
+        <v>-0.04162022115051282</v>
       </c>
       <c r="EY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.007104323850787648</v>
+        <v>0.1527275612065219</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.01284310668512889</v>
+        <v>0.02042587733285361</v>
       </c>
       <c r="FC2" t="n">
         <v>0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0.04212928341056942</v>
+        <v>0.004621926749034558</v>
       </c>
       <c r="FH2" t="n">
         <v>0</v>
@@ -1494,13 +1494,13 @@
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.06905343604800082</v>
+        <v>0.08168219624034039</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1933937195083247</v>
+        <v>0.1265006603352138</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>-0</v>
@@ -1512,34 +1512,34 @@
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.008751496330838247</v>
+        <v>0.001093792454329864</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.02975678931245693</v>
+        <v>0.2139486111355447</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.04917580125496394</v>
+        <v>0.05254398453344747</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
         <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.0245973674537824</v>
+        <v>-0.01853754530628432</v>
       </c>
       <c r="FZ2" t="n">
         <v>0</v>
@@ -1548,13 +1548,13 @@
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.01676400245010109</v>
+        <v>0.2147592548346046</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.506820416202598</v>
+        <v>0.200365798344334</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1512988315292321</v>
+        <v>-0.08816295660936643</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0894014669982037</v>
+        <v>-0.03423004713987846</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2727,25 +2727,25 @@
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3281030208409458</v>
+        <v>0.1834465555130934</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1438206327398314</v>
+        <v>-0.1329508406214016</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06650711979668926</v>
+        <v>-0.06877838247111151</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2763,76 +2763,76 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1636703380842824</v>
+        <v>0.05438848243362693</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.07082589306909623</v>
+        <v>-0.0351278893051179</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06861013235333138</v>
+        <v>-0.04903975666164105</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05205303412651781</v>
+        <v>-0.0567950302528558</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.02678039893502958</v>
+        <v>-0.131676308445377</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.05456789098434099</v>
+        <v>-0.02666438539943248</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.08252739456966764</v>
+        <v>0.07614968757337089</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.09311667938124972</v>
+        <v>-0.06539759157185819</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.07155184161350374</v>
+        <v>0.05899927690832815</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2841,55 +2841,55 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.6313985008618598</v>
+        <v>0.2390712920829497</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.0009671538772709405</v>
+        <v>-0.06242942348652803</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.07346296568910898</v>
+        <v>-0.1565037913229574</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1075536327159095</v>
+        <v>-0.001728966221439865</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1785100635379747</v>
+        <v>-0.03721018318189778</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.2178832512736839</v>
+        <v>0.005452059864653423</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,16 +2898,16 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1002720668292204</v>
+        <v>-0.00477324499648559</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1361023750103224</v>
+        <v>0.02986334196820952</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1399117610002128</v>
+        <v>0.06278418929006073</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
@@ -2919,103 +2919,103 @@
         <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1792924255309183</v>
+        <v>0.087711030569825</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.02728720487002694</v>
+        <v>-0.0559221049809719</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01847976450551139</v>
+        <v>-0.02184405752528305</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1693227804943385</v>
+        <v>-0.112851480488826</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01826662589373312</v>
+        <v>0.08951070727335779</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02675918665901609</v>
+        <v>0.01598400508935692</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02738416219267636</v>
+        <v>-0.02034642986842898</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.08359559011816739</v>
+        <v>0.08642464306639806</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.06075407163329826</v>
+        <v>0.001185026134364754</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.142857516540548</v>
+        <v>-0.1169512153052063</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.07658621094498133</v>
+        <v>0.09860061150823744</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.04139931429149234</v>
+        <v>0.02631651994716772</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3027,22 +3027,22 @@
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.05082810509893072</v>
+        <v>-0.07115332404564413</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1168623892593472</v>
+        <v>0.003734504493565217</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08920151630549029</v>
+        <v>-0.08611585180534345</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
@@ -3054,25 +3054,25 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1119684835902885</v>
+        <v>-0.05943393869982211</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0166562926384693</v>
+        <v>-0.005148644887689184</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.08033552884990094</v>
+        <v>-0.002240833982234111</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3087,76 +3087,76 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.09731820717538979</v>
+        <v>-0.03536097036297618</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0136698209407996</v>
+        <v>0.07701699280813717</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.002175222509651525</v>
+        <v>0.0172413502950076</v>
       </c>
       <c r="EB5" t="n">
         <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1374568369701569</v>
+        <v>-0.09252754702740749</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.01880636029074252</v>
+        <v>0.07828803819038554</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.06184552242369882</v>
+        <v>0.04829187652870463</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03128995038487917</v>
+        <v>-0.05160872111400606</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.01584578243602166</v>
+        <v>0.06436814415223244</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.01258702742849909</v>
+        <v>-0.008028439710100648</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,79 +3165,79 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1357092280183033</v>
+        <v>-0.1213928747363816</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.02738535119598975</v>
+        <v>0.1219306634917196</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02495997168107981</v>
+        <v>0.004863988233327929</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.004356556758884598</v>
+        <v>0.08848888450517198</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.02059320437733043</v>
+        <v>0.07044050459641638</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.0008013043855318308</v>
+        <v>0.04451660831671215</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.028769856418555</v>
+        <v>0.04993058258659484</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.04858183965051325</v>
+        <v>0.1498050009545524</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.07497687566319992</v>
+        <v>-0.01702461817221361</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
@@ -3246,22 +3246,22 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.1043139540051347</v>
+        <v>-0.08022046067784787</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.0867914094200988</v>
+        <v>0.08358179723751721</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.07574580990305529</v>
+        <v>0.1659637906262283</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,25 +3287,25 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03222863252999512</v>
+        <v>-0.00805114604141117</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.03834241363061266</v>
+        <v>-0.09933750017760834</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05918301025635688</v>
+        <v>0.1917284135353944</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,25 +3314,25 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02622500634335319</v>
+        <v>-0.06139952831800347</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.03560585833504224</v>
+        <v>-0.1068006127716514</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009569458067525788</v>
+        <v>0.07215367679531974</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,52 +3341,52 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.002499414233172883</v>
+        <v>-0.0767267632894134</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009552834913747213</v>
+        <v>-0.01041881951584561</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.003701274219213306</v>
+        <v>-0.03747123517765444</v>
       </c>
       <c r="AD6" t="n">
         <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.008362503566082841</v>
+        <v>-0.1568196021814557</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.00585555461237779</v>
+        <v>0.0280791153553038</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.004453908903863552</v>
+        <v>0.03240930171984829</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
@@ -3395,25 +3395,25 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.02245130020398232</v>
+        <v>-0.02454688284688492</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0042576185896654</v>
+        <v>-0.006904359520519311</v>
       </c>
       <c r="AQ6" t="n">
         <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.09441954386377933</v>
+        <v>0.2295169373554013</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,52 +3422,52 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01476482259284054</v>
+        <v>-0.1668164141229846</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01868352415241445</v>
+        <v>-0.1059612468437666</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02444684916958942</v>
+        <v>0.01836542076193581</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.05760316881359581</v>
+        <v>-0.00511084156611279</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.05623371557282792</v>
+        <v>-0.08128495438819551</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02608170207992497</v>
+        <v>0.02322451703499099</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,25 +3476,25 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01762010635297092</v>
+        <v>0.08140869462725041</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01574566319730343</v>
+        <v>0.0413952412134064</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.02484372477319048</v>
+        <v>0.08402465026080799</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.007868121996645046</v>
+        <v>-0.01876755786046879</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.007469743931104161</v>
+        <v>-0.06224562336597736</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3515,25 +3515,25 @@
         <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0203873256087943</v>
+        <v>-0.06831910706600465</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.003103448400292762</v>
+        <v>0.006140750039675162</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01999645567531992</v>
+        <v>0.07454476217097458</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
@@ -3545,103 +3545,103 @@
         <v>0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0005917581764394743</v>
+        <v>-0.0168163096204784</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.003073267481468285</v>
+        <v>0.03512650467491774</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.007325163895319055</v>
+        <v>0.02750297319192805</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.01438164583997744</v>
+        <v>-0.07229006698488413</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.00417517245556626</v>
+        <v>0.007980275879541296</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.02011418158760347</v>
+        <v>0.09502624220815947</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.003855100247764238</v>
+        <v>-0.03126318238095284</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.02537501496333749</v>
+        <v>-0.07790508672367717</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01053414234115276</v>
+        <v>0.06299969503033238</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.0004068853753831809</v>
+        <v>-0.0108836058275519</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.009184609220979988</v>
+        <v>-0.05308129980762548</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.0009440773418648769</v>
+        <v>0.01241611980283096</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3650,55 +3650,55 @@
         <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.03592186479620006</v>
+        <v>-0.003256454242833304</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01511872580250104</v>
+        <v>-0.02670866777920386</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.02161658552178343</v>
+        <v>0.06281247649899513</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.02309081079837524</v>
+        <v>-0.03206465655783516</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.005808472753741817</v>
+        <v>0.006428689785008042</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.02088522362134528</v>
+        <v>0.02859726422991957</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
@@ -3707,22 +3707,22 @@
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.003651672950796888</v>
+        <v>-0.02108820565391826</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01428059629850453</v>
+        <v>0.003117933633379079</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.001039945193238078</v>
+        <v>0.0770637005192753</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,28 +3731,28 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.01408867330667576</v>
+        <v>-0.07879308892642199</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.009568043530420617</v>
+        <v>-0.01259914012943532</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.02244727867675199</v>
+        <v>0.06796679298630742</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3764,25 +3764,25 @@
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.0172001859272529</v>
+        <v>0.118407807144223</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.01062282213024402</v>
+        <v>-0.03381851296092879</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.005812112691809729</v>
+        <v>0.09685622895775299</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.007573395310806696</v>
+        <v>0.02503777611327987</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
@@ -3800,46 +3800,46 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.01660380050588882</v>
+        <v>-0.05417533859437635</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0163570725718126</v>
+        <v>-0.07266167463093466</v>
       </c>
       <c r="FV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.003374934830430797</v>
+        <v>-0.02731249354804582</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.007527326768514248</v>
+        <v>0.08950277175827855</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,25 +3847,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4560203791137082</v>
+        <v>0.237988397356176</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1191726632923397</v>
+        <v>-0.07406863476634669</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1246238288012107</v>
+        <v>-0.01988875636873827</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3874,22 +3874,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3109697210267965</v>
+        <v>0.2623964600715016</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1101520934483003</v>
+        <v>-0.0994283181882142</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.09309818454073726</v>
+        <v>-0.05890353025321923</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3901,70 +3901,70 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1272378730593008</v>
+        <v>0.05905180486682099</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0423394313341354</v>
+        <v>-0.02733697764869215</v>
       </c>
       <c r="W7" t="n">
-        <v>0.112485184428685</v>
+        <v>-0.065868281801178</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05033190370403064</v>
+        <v>-0.03853131147879141</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.007669813721382654</v>
+        <v>-0.1180370765930241</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.02891133705097918</v>
+        <v>-0.01418567224968354</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04012783437829444</v>
+        <v>0.07423210774985285</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.05214898450704054</v>
+        <v>-0.06751390575472353</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06312373335009729</v>
+        <v>0.07159534393765764</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3979,55 +3979,55 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5618150716088457</v>
+        <v>0.2425019229882082</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.04243648738210168</v>
+        <v>-0.05411702369389637</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.04832908917313785</v>
+        <v>-0.1511910245106227</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.08118559746355276</v>
+        <v>0.01547056159877016</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1792315763962275</v>
+        <v>-0.04220303214718579</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1638335891531407</v>
+        <v>-0.0005638350439585573</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1467585076903564</v>
+        <v>-0.01820999803020832</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1025033420934734</v>
+        <v>0.02747768712321996</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1684456950711455</v>
+        <v>0.08706763593618448</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
@@ -4057,103 +4057,103 @@
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1569418276639266</v>
+        <v>0.08800950762215601</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.001234405415390258</v>
+        <v>-0.04070676646456709</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02114289184515704</v>
+        <v>-0.01829310691326632</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1364523880912543</v>
+        <v>-0.1102954741485053</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.01593437886435398</v>
+        <v>0.07721192819344268</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0001472034763176676</v>
+        <v>0.005439488668460606</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.005405350070254285</v>
+        <v>-0.03080255980543999</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.07553653094256396</v>
+        <v>0.07911838652370169</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.07312124602062256</v>
+        <v>0.008430770892701389</v>
       </c>
       <c r="CR7" t="n">
         <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.09305884893300372</v>
+        <v>-0.1120404307833316</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0410006384071785</v>
+        <v>0.08428999165622066</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01589988637875427</v>
+        <v>0.01622047363019851</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4162,25 +4162,25 @@
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.01645453524315078</v>
+        <v>-0.06345854290223693</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.09262447410802493</v>
+        <v>-0.001257595674364157</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03033667662861024</v>
+        <v>-0.03801586628224633</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4192,25 +4192,25 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.1238952924929561</v>
+        <v>-0.05277205720660934</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.02429273323575949</v>
+        <v>-0.04863434967850475</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.06795262523074022</v>
+        <v>-0.06364337865985414</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,19 +4225,19 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.08280868064574037</v>
+        <v>-0.02086693051271751</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.03620472255545056</v>
+        <v>0.04662315113810003</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001269630666195115</v>
+        <v>-0.006694449083984843</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4246,76 +4246,76 @@
         <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1120003827645459</v>
+        <v>-0.08501363463640468</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0002292147476986073</v>
+        <v>0.05830507296047705</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.088496057036861</v>
+        <v>0.0485592990587673</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.009223540851360602</v>
+        <v>-0.03964640488294156</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.008252254054124268</v>
+        <v>0.01264292639968359</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.04032703175097099</v>
+        <v>0.01245217913746397</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.08944148920511914</v>
+        <v>-0.1153103708716682</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.005175708238250683</v>
+        <v>0.1045664482350886</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0185227474102873</v>
+        <v>-0.008490570959977975</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4324,25 +4324,25 @@
         <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04991696124130957</v>
+        <v>0.1066987668516167</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.002008894591194805</v>
+        <v>0.07728661449480757</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.003623766167446728</v>
+        <v>0.00579252558993922</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
@@ -4354,49 +4354,49 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.05389705048680056</v>
+        <v>0.03724988268477734</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.02955512453738037</v>
+        <v>0.1431163511756597</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.1061943218738938</v>
+        <v>-0.03495335437764527</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.09583008573009355</v>
+        <v>-0.0692911670149999</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.08244775888907108</v>
+        <v>0.02746721605727306</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
         <v>-0</v>
@@ -4408,15 +4408,15 @@
         <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1194906980511484</v>
+        <v>0.2908743448842169</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04538258791788243</v>
+        <v>0.06090864797709119</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1060676843250774</v>
+        <v>-0.2914701659397343</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09252808125432513</v>
+        <v>0.3601420452881356</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,16 +4452,16 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.01331453499912601</v>
+        <v>-0.06356704487929905</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.08601883698931477</v>
+        <v>-0.2858123438532018</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02417774931799993</v>
+        <v>0.060179925385843</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,40 +4479,40 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.02519406860647332</v>
+        <v>-0.1222506647392484</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0001621411500019293</v>
+        <v>-0.1294345365550936</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.007898924772483643</v>
+        <v>-0.09992703261143562</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.005915520365239308</v>
+        <v>-0.1742700837699027</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.004439580105144186</v>
+        <v>0.04618807474599891</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4524,25 +4524,25 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.03593502062855048</v>
+        <v>0.1168776963250445</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.01358709418525111</v>
+        <v>-0.02721581533219997</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.02558114158990644</v>
+        <v>-0.1287270766135116</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
@@ -4551,46 +4551,46 @@
         <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1242922100013443</v>
+        <v>0.5976372389840959</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.06352238331781064</v>
+        <v>-0.235573942495631</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1062147378654205</v>
+        <v>-0.2536095240449097</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.03694514092672558</v>
+        <v>-0.1278051245478212</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.03323570572489835</v>
+        <v>0.05911512473431856</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.0486212010586583</v>
+        <v>-0.1082497287502834</v>
       </c>
       <c r="BI8" t="n">
         <v>0</v>
@@ -4602,10 +4602,10 @@
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.03716092023107177</v>
+        <v>0.1224918416374395</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
@@ -4614,25 +4614,25 @@
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.007521854115291301</v>
+        <v>0.05050728994160632</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0.0008198796342343268</v>
+        <v>0.1382442761663326</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.02960873057947865</v>
+        <v>0.1911933919562708</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,16 +4641,16 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.0287530358911635</v>
+        <v>-0.03990962301838557</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.03646328291012496</v>
+        <v>-0.1777228573941068</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>-0</v>
@@ -4659,19 +4659,19 @@
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.02538445453907556</v>
+        <v>-0.1464907028313842</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002008766886375961</v>
+        <v>0.01858241987809645</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04364388652348777</v>
+        <v>0.1374425799395702</v>
       </c>
       <c r="CJ8" t="n">
         <v>-0</v>
@@ -4680,52 +4680,52 @@
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.005677485740793072</v>
+        <v>-0.1052069994230613</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.008567427391484703</v>
+        <v>0.1148831113805469</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.008252129228281807</v>
+        <v>-0.002621605785241416</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.02217506018664159</v>
+        <v>-0.1384094784177018</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0008308610522224213</v>
+        <v>0.01876391754266498</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04895950498286161</v>
+        <v>0.1607625240399201</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -4734,25 +4734,25 @@
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.009302180731053889</v>
+        <v>-0.1405229066586219</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05541174839478513</v>
+        <v>-0.07026486454167997</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.003794604839087541</v>
+        <v>0.0307715442447543</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,13 +4761,13 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.003229431030354295</v>
+        <v>-0.1302894344163416</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
@@ -4776,16 +4776,16 @@
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01563345646498519</v>
+        <v>0.03614657144389817</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.009077827972945393</v>
+        <v>0.2214394828109857</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,25 +4794,25 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.0350143366916657</v>
+        <v>-0.005839749325615324</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.01249976484230127</v>
+        <v>0.0837233475740075</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.04182547911309271</v>
+        <v>0.05814712221513715</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
@@ -4821,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.02782162175200936</v>
+        <v>-0.09509455860996861</v>
       </c>
       <c r="EH8" t="n">
         <v>-0</v>
@@ -4830,40 +4830,40 @@
         <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0002360768313014737</v>
+        <v>-0.03223052521722963</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.04867129685946653</v>
+        <v>0.0294592880656751</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.009155441899093597</v>
+        <v>-0.04254554856415322</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01017714918631951</v>
+        <v>-0.1072744432857883</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.009055903376728142</v>
+        <v>-0.03835205870846214</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,106 +4875,106 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.01837062270953727</v>
+        <v>-0.1588437257592235</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.005674906055468013</v>
+        <v>-0.006981530266663791</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04319432907627201</v>
+        <v>0.1474443433525114</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.01481857746247571</v>
+        <v>0.1343400778700122</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0008034044519451116</v>
+        <v>-0.01981621883457654</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03457919844951835</v>
+        <v>0.1031845276322424</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.001245997734627829</v>
+        <v>0.1121204015824177</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.03109227689967041</v>
+        <v>-0.02133830595318835</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.05333200035334506</v>
+        <v>0.02850236043599252</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01064855719178364</v>
+        <v>-0.008523754079290799</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.004874948921817543</v>
+        <v>0.1916916071825132</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
         <v>-0</v>
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1019117481666127</v>
+        <v>0.2992608581337967</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,16 +4994,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04562600082483012</v>
+        <v>0.02413787549111208</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08590017957647095</v>
+        <v>-0.174347362607376</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.09119496520188833</v>
+        <v>0.3633871836868635</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,16 +5021,16 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02954614851232955</v>
+        <v>-0.07185643853850092</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.05998112290388039</v>
+        <v>-0.1530745698135873</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01164796016002569</v>
+        <v>0.1030504873918069</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,37 +5048,37 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.009946405238814548</v>
+        <v>-0.1442072490135353</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01680434133714383</v>
+        <v>-0.04242751744867003</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.01118813592439956</v>
+        <v>-0.05694005799226985</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0007466142246327459</v>
+        <v>-0.2329686256389652</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.004589056584121867</v>
+        <v>0.07233939375495201</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5093,22 +5093,22 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01276871327755899</v>
+        <v>0.03165869049150068</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.02430631694893935</v>
+        <v>-0.04571815398600138</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.002820544235132121</v>
+        <v>0.006620013987002642</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
@@ -5117,37 +5117,37 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1091856965071546</v>
+        <v>0.3813010838771438</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.03748988285653773</v>
+        <v>-0.2532697963684561</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.0474782303129833</v>
+        <v>-0.1831279605465449</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03358181153526307</v>
+        <v>-0.01335458276372954</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,13 +5156,13 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.04794027450527292</v>
+        <v>0.02397663573219059</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.07020347915159861</v>
+        <v>-0.09644955689177781</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
         <v>-0</v>
@@ -5171,10 +5171,10 @@
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03668971782635744</v>
+        <v>0.03832657706331073</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,25 +5183,25 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01356204953244396</v>
+        <v>0.08593284364453815</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.02683996189946957</v>
+        <v>-0.0001487831819218415</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.03175236465464855</v>
+        <v>0.1268955525743105</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.009874276974335756</v>
+        <v>-0.03807307723523048</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.008000848394761131</v>
+        <v>-0.05344837048092462</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5222,40 +5222,40 @@
         <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.02088247333688549</v>
+        <v>-0.1170778834737625</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.005240114736717657</v>
+        <v>0.009896556308490305</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.02908609164144044</v>
+        <v>0.07600676043785325</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.004571943911391039</v>
+        <v>-0.04471119289135073</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
@@ -5264,64 +5264,64 @@
         <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.006487817169739947</v>
+        <v>0.1081328448611289</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.005065132143143217</v>
+        <v>0.08924995455929224</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.01323898798019688</v>
+        <v>-0.118214153791337</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.006498621195839063</v>
+        <v>0.008135626061926006</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.03011508169357524</v>
+        <v>0.09770345248432717</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01075625517884751</v>
+        <v>-0.05571755474548189</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.04725011580701986</v>
+        <v>-0.189585658097067</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0.003197738894053326</v>
+        <v>0.0395823670404679</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5336,19 +5336,19 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0006128007412766327</v>
+        <v>-0.01061433088055317</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.007272711697786836</v>
+        <v>-0.1081527882048107</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.01397501561629381</v>
+        <v>0.08681856265423332</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
@@ -5357,13 +5357,13 @@
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03660958086851607</v>
+        <v>-0.01130627877708737</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,64 +5372,64 @@
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01672688898505799</v>
+        <v>-0.0305344082889541</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.02101258781534183</v>
+        <v>0.02874981172678095</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.02482948653957689</v>
+        <v>-0.068086859491981</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.001572707540105759</v>
+        <v>0.01545234550941605</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.03751294448049863</v>
+        <v>0.009426610765460594</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001386093192979879</v>
+        <v>-0.02390362791105904</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.02073609096832773</v>
+        <v>0.01265030493619056</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.007534983483790549</v>
+        <v>0.1489776295732418</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
@@ -5438,13 +5438,13 @@
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.01204010382442314</v>
+        <v>-0.1291850640357427</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
@@ -5453,43 +5453,43 @@
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01066225538279482</v>
+        <v>-0.01369403304986798</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.03313395539609962</v>
+        <v>0.06523362376335676</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.01838408877973874</v>
+        <v>0.2023619812627934</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.005933800781193055</v>
+        <v>-0.05569636352861895</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.003311404596918152</v>
+        <v>0.1739556608198649</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.009182508353747102</v>
+        <v>0.06466462698415207</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
@@ -5507,46 +5507,46 @@
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.01793210089397788</v>
+        <v>-0.08597158570783005</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0151665466470535</v>
+        <v>-0.05185876562404261</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.00516924183354349</v>
+        <v>-0.04463639683860129</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.004917632413180261</v>
+        <v>0.08954937507941602</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,22 +5554,22 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.449737565258405</v>
+        <v>0.334653392645315</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1105046333931457</v>
+        <v>-0.144404684033647</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.06264448288242515</v>
+        <v>-0.03345538584708935</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3291518694469547</v>
+        <v>0.3568373235564137</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.08964385874323494</v>
+        <v>-0.1504091846552977</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06251897768483629</v>
+        <v>-0.07947691300855093</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5605,28 +5605,28 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1166340421384599</v>
+        <v>0.07098351425858539</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0003669408841699511</v>
+        <v>-0.02972918111255924</v>
       </c>
       <c r="W10" t="n">
-        <v>0.06163670748069955</v>
+        <v>-0.07379452297752039</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,43 +5635,43 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1433434825568488</v>
+        <v>-0.07712592527499081</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01961857442003052</v>
+        <v>-0.1109278317586398</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.08757633248848125</v>
+        <v>-0.1152977500088811</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.04265522079927963</v>
+        <v>0.1293028302620697</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.09269306029650923</v>
+        <v>-0.09997396830704497</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.05555179727076654</v>
+        <v>0.02673031679871844</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4541626509940474</v>
+        <v>0.3707870590936507</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.0307720555014558</v>
+        <v>-0.179617982223529</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1369112820278222</v>
+        <v>-0.233629612564022</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,25 +5707,25 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02832795993562646</v>
+        <v>-0.03831086364765685</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.04447679403625763</v>
+        <v>-0.04436671382915593</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2256646256631672</v>
+        <v>0.002544065024679682</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,85 +5734,85 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.01631085168759223</v>
+        <v>0.01489973151027933</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1120875788853284</v>
+        <v>0.05727795634698189</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1238934374747671</v>
+        <v>0.03343688373573023</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1444643672499385</v>
+        <v>0.1652783957481185</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.004258560489198703</v>
+        <v>-0.06182818049924221</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03317928548945379</v>
+        <v>-0.02837511186025098</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1118568378400838</v>
+        <v>-0.125149099188709</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01761667244827174</v>
+        <v>0.1338056174217989</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01100582683321509</v>
+        <v>-0.004386293267039801</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5821,28 +5821,28 @@
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.008400036684102934</v>
+        <v>-0.08135334495648865</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.08675364367323225</v>
+        <v>0.1506479445626191</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.07227742322251231</v>
+        <v>0.03791180025699192</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
         <v>-0</v>
@@ -5851,22 +5851,22 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1005669351094852</v>
+        <v>-0.1201722409248486</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0439597153505891</v>
+        <v>0.1465838768340866</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.009340895970640599</v>
+        <v>0.01423467380297736</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
         <v>-0</v>
@@ -5878,22 +5878,22 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.009492100051810023</v>
+        <v>-0.1194071346803438</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.004725703634261891</v>
+        <v>-0.01268725945125371</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.03065408289940102</v>
+        <v>-0.0647190489624388</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5902,25 +5902,25 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.08139158515880159</v>
+        <v>-0.064806489184582</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.1045421119972278</v>
+        <v>0.05421689383884704</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.07155691946303325</v>
+        <v>-0.03149920006072369</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
@@ -5929,19 +5929,19 @@
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01555584846411274</v>
+        <v>-0.002039461655394726</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.0196819452615177</v>
+        <v>0.07658708377166348</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.004438258455498592</v>
+        <v>-0.03147148821820058</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
@@ -5950,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
@@ -5959,22 +5959,22 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.07101316737130832</v>
+        <v>-0.07434217900062905</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0433171201577944</v>
+        <v>0.1065805975996825</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.09315084938409131</v>
+        <v>0.02823390961924768</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,25 +5983,25 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.104554312603871</v>
+        <v>-0.07926732877847251</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.08423423363571388</v>
+        <v>-0.08543697936442093</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.02448844109790163</v>
+        <v>-0.0008437834568815849</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6010,25 +6010,25 @@
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1002110786306688</v>
+        <v>-0.1379619335510558</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.03407814338964078</v>
+        <v>0.1629837745237964</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.0173960277136179</v>
+        <v>-0.009217305379346544</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
@@ -6040,49 +6040,49 @@
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.01290260148865548</v>
+        <v>0.1157473232960236</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.07782985402148417</v>
+        <v>0.09258908988832289</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.007880217947628913</v>
+        <v>-0.00749566494422444</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.004574938564115501</v>
+        <v>0.03393611270359898</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.1131974160164583</v>
+        <v>0.1824154898390282</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.02889058601804562</v>
+        <v>-0.04033446426173678</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
         <v>0</v>
@@ -6091,39 +6091,39 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01100635298369736</v>
+        <v>-0.07969939750730445</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.05322568138151754</v>
+        <v>0.06426240441694228</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2755258249281843</v>
+        <v>0.405020222265589</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06492836816048551</v>
+        <v>0.06372926250152276</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.204497133225938</v>
+        <v>-0.4251100896151447</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6144,13 +6144,13 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2394854609441788</v>
+        <v>0.4317521272632124</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,64 +6159,64 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.00970790053260227</v>
+        <v>-0.1198726529183301</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1432068252116536</v>
+        <v>-0.3997806439462324</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02571055178553928</v>
+        <v>0.1281639823399459</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.04328334879629617</v>
+        <v>-0.05703276540578284</v>
       </c>
       <c r="X11" t="n">
-        <v>0.002470851453459564</v>
+        <v>-0.1037767909528199</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.01158050473226523</v>
+        <v>-0.1095799857789832</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001070190356738853</v>
+        <v>-0.2468683596267923</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.03081253672139382</v>
+        <v>0.1103358290962077</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -6231,19 +6231,19 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03161417360884488</v>
+        <v>0.1310487906846777</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0183896328089442</v>
+        <v>-0.02074229970055991</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.06362833186277897</v>
+        <v>-0.1026254462108533</v>
       </c>
       <c r="AQ11" t="n">
         <v>-0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2061149687676839</v>
+        <v>0.5732363015967256</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.05133443669933167</v>
+        <v>-0.3068647865287035</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.1431815344385163</v>
+        <v>-0.417826589388127</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.07525200905589015</v>
+        <v>-0.07260255830645147</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,25 +6294,25 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.05893207595619136</v>
+        <v>0.06339971310477943</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.08903067774101013</v>
+        <v>-0.07013979051847419</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
         <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.06008887002168575</v>
+        <v>0.08911388918297611</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,25 +6321,25 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.02767248257505334</v>
+        <v>0.04057829006772086</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01948861954788203</v>
+        <v>0.08548936850812554</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.0725249700044187</v>
+        <v>0.1968008826689391</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,37 +6348,37 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01917982713248319</v>
+        <v>-0.02665386706205927</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.02567385600338756</v>
+        <v>-0.1309997434669045</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.05646449051392896</v>
+        <v>-0.1548475551947182</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.003965315100631192</v>
+        <v>0.03987324885462569</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.05767913336282289</v>
+        <v>0.138204725059459</v>
       </c>
       <c r="CJ11" t="n">
         <v>-0</v>
@@ -6393,46 +6393,46 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.002615165114181482</v>
+        <v>-0.1327519335459714</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.001456018823493317</v>
+        <v>0.1928771426723679</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.0437817946841828</v>
+        <v>-0.01963679564291157</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.05101108946540956</v>
+        <v>-0.1527453425625379</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.002304887530023189</v>
+        <v>0.0346123183211647</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.06143717171175294</v>
+        <v>0.1731155248870737</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
@@ -6441,40 +6441,40 @@
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.007061867433795261</v>
+        <v>0.02708209637042656</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0811188553538793</v>
+        <v>-0.07061649321783686</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.845195236035354e-05</v>
+        <v>0.05100448248911048</v>
       </c>
       <c r="DK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.02867783031109391</v>
+        <v>-0.1229682322830714</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
@@ -6483,16 +6483,16 @@
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01433278288697825</v>
+        <v>0.002414312099513621</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.01105013427159111</v>
+        <v>0.1647295397777635</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,46 +6501,46 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.05137517834268427</v>
+        <v>-0.02048394194962008</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.02718044773268719</v>
+        <v>0.06656946150919971</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.03947245291474771</v>
+        <v>0.07739911502049111</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.05248015543422756</v>
+        <v>-0.06439102698223909</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01539468396701377</v>
+        <v>-0.02870277182391009</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.06455462074961942</v>
+        <v>0.03985231897036959</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6549,13 +6549,13 @@
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.03434589067990546</v>
+        <v>-0.07513553425988762</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
@@ -6564,13 +6564,13 @@
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.01263472047024843</v>
+        <v>-0.105349038891563</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0.01302188632892642</v>
+        <v>0.0087581709705711</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6582,61 +6582,61 @@
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.04944928083076845</v>
+        <v>-0.1703418725999054</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.00466098849454194</v>
+        <v>0.009225280432878194</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.05740051153665914</v>
+        <v>0.1538711331049554</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.01390280895665056</v>
+        <v>0.1449232269162577</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.005721239776736639</v>
+        <v>-0.07478144136033103</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03089961845139688</v>
+        <v>0.1793862669391168</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.004318561172450252</v>
+        <v>0.06161370376982636</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.02830880490512632</v>
+        <v>-0.07613790300248933</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.03562895596549798</v>
+        <v>-0.02554206156088053</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0009116652555951593</v>
+        <v>-0.04589258961790669</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.0119843347930833</v>
+        <v>0.2223288923140189</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,73 +6692,73 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3694532871327955</v>
+        <v>0.2364146927472041</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1201493077321622</v>
+        <v>-0.09837540476265959</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.106078842256138</v>
+        <v>0.02851122526489636</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.06317956264779863</v>
+        <v>-0.06387116679465267</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.301358449371957</v>
+        <v>0.254184366338777</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.07613095210577185</v>
+        <v>-0.1224331013470458</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05791112078894675</v>
+        <v>-0.03197710576783411</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.06611399102013746</v>
+        <v>-0.05162251531902547</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.07079111034847746</v>
+        <v>0.08401946622941955</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.02017491081063709</v>
+        <v>-0.04217034143666364</v>
       </c>
       <c r="W12" t="n">
-        <v>0.08124882569074741</v>
+        <v>-0.07806677351703899</v>
       </c>
       <c r="X12" t="n">
-        <v>0.006748867212271283</v>
+        <v>-0.06139117091868761</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,130 +6770,130 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04886617283242344</v>
+        <v>-0.08685651743526977</v>
       </c>
       <c r="AD12" t="n">
         <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.01998521909183749</v>
+        <v>-0.09928873311900148</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02584883717397595</v>
+        <v>-0.06423473805694452</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.01934232954904554</v>
+        <v>0.05253266170165188</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01425278365764937</v>
+        <v>0.05456446555349607</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.05885032735386687</v>
+        <v>-0.05401016610294541</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.0596792208175272</v>
+        <v>0.05293413071124901</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.03734451094494778</v>
+        <v>-0.04178089429491233</v>
       </c>
       <c r="AQ12" t="n">
         <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3238331730917484</v>
+        <v>0.2589582496575185</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.04324848198620739</v>
+        <v>-0.03865904802062076</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.02937239900335384</v>
+        <v>-0.08495768189844166</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.04375711516681704</v>
+        <v>-0.1012780541015261</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.05167348632288866</v>
+        <v>-0.01770658421516293</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.07955093118622197</v>
+        <v>-0.08935826977796767</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1116914058386765</v>
+        <v>-0.05136052699201238</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.08414606449034499</v>
+        <v>-0.02943070881785713</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.08000416037114691</v>
+        <v>-0.03369542269308888</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.05586068237683024</v>
+        <v>0.0599254880853754</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1194637593794258</v>
+        <v>0.03266745860365652</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.03031989054633144</v>
+        <v>-0.01004145317464008</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6902,31 +6902,31 @@
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.08673212658926806</v>
+        <v>0.1030469887164834</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.004593398800621502</v>
+        <v>-0.02348014960754849</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0112214419673465</v>
+        <v>0.01280975867306597</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.006185778035645527</v>
+        <v>-0.0512139128121379</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
@@ -6935,25 +6935,25 @@
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.07796029241944803</v>
+        <v>-0.07789571400717461</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.004703188963560567</v>
+        <v>0.06550721315157947</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.0003753740793287614</v>
+        <v>-0.00869242503377236</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.03129531144653609</v>
+        <v>0.0163940789725587</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL12" t="n">
         <v>0</v>
@@ -6962,52 +6962,52 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.003379435663676963</v>
+        <v>-0.03263598111338146</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.06312649354337084</v>
+        <v>0.1291507341554377</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.08108015070047044</v>
+        <v>0.05552105185600111</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.05087378597665723</v>
+        <v>0.04621832899427842</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.059855303919773</v>
+        <v>-0.07626805400467351</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.03183717778404103</v>
+        <v>0.06971559885572035</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.002623548317212002</v>
+        <v>0.002591181498692777</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.03268192620317573</v>
+        <v>0.02576436495008021</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD12" t="n">
         <v>-0</v>
@@ -7016,19 +7016,19 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.0150351806050066</v>
+        <v>-0.03116490280688861</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0564800070019654</v>
+        <v>0.009430095180138534</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.005448230357230063</v>
+        <v>0.01216448602918218</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.02160291818655201</v>
+        <v>0.02508927375329784</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7037,25 +7037,25 @@
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.0128089280286045</v>
+        <v>-0.01073319957144691</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.06238227727532547</v>
+        <v>0.009511293617483534</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.02187132213573931</v>
+        <v>-0.0617665500131073</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.02726149558088034</v>
+        <v>0.01667140986909774</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7067,76 +7067,76 @@
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.04829024479286884</v>
+        <v>-0.008228068708022567</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.0241358802354509</v>
+        <v>0.07063915115054735</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0342973578962124</v>
+        <v>-0.002605545486912772</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.05845071095831052</v>
+        <v>0.004331529449029596</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.08772061378131157</v>
+        <v>-0.06236104616112521</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.03882054561856284</v>
+        <v>0.05119716491637583</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.06614520598718032</v>
+        <v>0.03604327099915579</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.02208907225157403</v>
+        <v>-0.04267069066468405</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03981605130173743</v>
+        <v>-0.02639969140344399</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.007158178357422127</v>
+        <v>0.0430085845233904</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02468534606957337</v>
+        <v>-0.01755936430917555</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.03358515721009882</v>
+        <v>0.03755110331030392</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7151,19 +7151,19 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.06065417263721548</v>
+        <v>-0.08006886639634073</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.004564047750212546</v>
+        <v>0.08965074870474331</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01401243305891759</v>
+        <v>-0.02324592613762326</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.03741622161092956</v>
+        <v>0.02148876749303454</v>
       </c>
       <c r="FD12" t="n">
         <v>0</v>
@@ -7178,22 +7178,22 @@
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02967019244927751</v>
+        <v>0.0980303005363611</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.05619489250679095</v>
+        <v>0.05368462444065113</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.01414901746846079</v>
+        <v>0.01392432313397117</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0.008732920427275265</v>
+        <v>0.07589248088999746</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7202,52 +7202,52 @@
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.004005238507743286</v>
+        <v>0.009737843138777947</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01703143380890867</v>
+        <v>0.1013308913174651</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.03725680590032083</v>
+        <v>-0.02508659213508916</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.03919955839753179</v>
+        <v>-0.03045687956525964</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.04031895800977078</v>
+        <v>-0.06806121882885464</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.07569762397205471</v>
+        <v>0.03286297300467071</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.04165466825632142</v>
+        <v>0.04816472334260115</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
@@ -7261,49 +7261,49 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3438116639870767</v>
+        <v>0.2318319737746851</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06668499094194343</v>
+        <v>-0.1055342469314975</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0364752059208738</v>
+        <v>-0.01826382788248208</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2323967045121962</v>
+        <v>0.2763805201083936</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.09179077263011975</v>
+        <v>-0.1282710006845446</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.04690605313107066</v>
+        <v>-0.04838170570842442</v>
       </c>
       <c r="O13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -7315,70 +7315,70 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.08384865396667288</v>
+        <v>0.03489870195414244</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.04808717573136204</v>
+        <v>-0.02955779122174678</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1302540369275459</v>
+        <v>-0.03447426939228827</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1021263351355602</v>
+        <v>-0.04546890398287862</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.002319977227769498</v>
+        <v>-0.08307840441950014</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.05504551930785918</v>
+        <v>-0.05270080153236473</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.0440260401992733</v>
+        <v>0.06569261949474377</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.05345836035298392</v>
+        <v>-0.06676239146808574</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.02217558500385006</v>
+        <v>0.04631976780846992</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -7387,61 +7387,61 @@
         <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.3183908640638838</v>
+        <v>0.2020124348634385</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1359442842659188</v>
+        <v>-0.06150445624175509</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1518271900009334</v>
+        <v>-0.09734708410111427</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.02185101578438996</v>
+        <v>0.002414354013821389</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.1623377606079976</v>
+        <v>-0.03214516521234582</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1230685023028073</v>
+        <v>-0.02160564728555752</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,19 +7450,19 @@
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.07898677758722253</v>
+        <v>-0.01120924440666267</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0.007315093255475858</v>
+        <v>0.02818316512118992</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1919122380428723</v>
+        <v>0.04673940525191485</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
         <v>0</v>
@@ -7471,52 +7471,52 @@
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.09011057133532482</v>
+        <v>0.0829281413352994</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0357838536480021</v>
+        <v>-0.02705555456839545</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.06454587293008848</v>
+        <v>-0.002999897531873651</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.08206121575279821</v>
+        <v>-0.0733646452156498</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.0203963756565792</v>
+        <v>0.06159618501766827</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.006300761843916369</v>
+        <v>-0.0009103893594305519</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
         <v>0</v>
@@ -7525,28 +7525,28 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.02187097891290269</v>
+        <v>-0.06205662152109965</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.1317712049625057</v>
+        <v>0.1295158182323</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.1063684947281441</v>
+        <v>0.02147557524763602</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
@@ -7555,46 +7555,46 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.05614421835079308</v>
+        <v>-0.07117176142385044</v>
       </c>
       <c r="CX13" t="n">
         <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0006052411601386537</v>
+        <v>0.06560921014392193</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01317283812819755</v>
+        <v>0.005913490920410524</v>
       </c>
       <c r="DA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.04278183918028314</v>
+        <v>-0.03913399489548414</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.03334621375761366</v>
+        <v>0.03238580998184849</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02206517767788532</v>
+        <v>-0.03447324244154491</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7612,19 +7612,19 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.05080086482455457</v>
+        <v>-0.03439240062418648</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.04777858819569205</v>
+        <v>-0.01607710996810241</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.04271040790145936</v>
+        <v>-0.02112949349694825</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7633,76 +7633,76 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.02947476765106043</v>
+        <v>-0.007801919706635443</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.03289909360897093</v>
+        <v>0.0628476793267192</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.009759899830155542</v>
+        <v>-0.02512874572365525</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.07423666022869602</v>
+        <v>-0.05409224841650533</v>
       </c>
       <c r="EH13" t="n">
         <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0.009668036159286261</v>
+        <v>0.03876122441688517</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.08872154828900254</v>
+        <v>0.04076131206668748</v>
       </c>
       <c r="EK13" t="n">
         <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.02431342131128654</v>
+        <v>-0.02536020060621257</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0211258344564127</v>
+        <v>0.03321822580961781</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02315041085613775</v>
+        <v>-0.01566186482625262</v>
       </c>
       <c r="ET13" t="n">
         <v>0</v>
@@ -7714,49 +7714,49 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.05731144194823702</v>
+        <v>-0.07885366847354572</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.03122942534572026</v>
+        <v>0.07870547335953963</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.006817645584025781</v>
+        <v>-0.008728431344551394</v>
       </c>
       <c r="FC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD13" t="n">
         <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.008675601325849625</v>
+        <v>0.07779627601608774</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.001945876880924079</v>
+        <v>0.04703506880186738</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.02869794252845428</v>
+        <v>-0.007633789709656887</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
@@ -7768,25 +7768,25 @@
         <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.002210654611916264</v>
+        <v>0.001937685013807634</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.02217272212118767</v>
+        <v>0.07149436428610489</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.004905419685142409</v>
+        <v>-0.009594951381279391</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
@@ -7798,39 +7798,39 @@
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01287889391507899</v>
+        <v>-0.05193053893176117</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.1154313790071256</v>
+        <v>0.0179541372701983</v>
       </c>
       <c r="GC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.3315543892809102</v>
+        <v>-0.165568207106956</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
@@ -7839,25 +7839,25 @@
         <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07666755896090115</v>
+        <v>0.07884927677811288</v>
       </c>
       <c r="F14" t="n">
-        <v>1.033044029201602</v>
+        <v>0.3127735476485545</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2935583711115533</v>
+        <v>-0.2198368725511436</v>
       </c>
       <c r="L14" t="n">
         <v>-0</v>
@@ -7866,13 +7866,13 @@
         <v>-0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.07009031831491096</v>
+        <v>0.1515340633234578</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8574417820790873</v>
+        <v>0.4114495195932215</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.005335767159138302</v>
+        <v>-0.1071091432611775</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
@@ -7893,10 +7893,10 @@
         <v>-0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1604568618313796</v>
+        <v>0.05877261611779534</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1492988004105616</v>
+        <v>0.08366313484153308</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -7908,91 +7908,91 @@
         <v>-0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.01367738674115263</v>
+        <v>0.02512261364540485</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.04846916225135422</v>
+        <v>0.1616423925520302</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.03838207396274902</v>
+        <v>-0.006248983035295521</v>
       </c>
       <c r="AH14" t="n">
         <v>-0</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK14" t="n">
         <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.03474040686563112</v>
+        <v>-0.06091622371524009</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.0224477170635593</v>
+        <v>0.01742784635275039</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.1700032004544386</v>
+        <v>0.08255684735471984</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.2221876145571115</v>
+        <v>-0.2650127663948265</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW14" t="n">
         <v>-0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.2734928770113581</v>
+        <v>0.1366306246068647</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.7825007548973365</v>
+        <v>0.2348793137059716</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
         <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.1171302075292977</v>
+        <v>0.1359001061410542</v>
       </c>
       <c r="BE14" t="n">
         <v>-0</v>
@@ -8001,10 +8001,10 @@
         <v>-0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.05348463471216348</v>
+        <v>0.05232032298091423</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.1865724259514154</v>
+        <v>-0.002928266459616007</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
@@ -8013,40 +8013,40 @@
         <v>0</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.1720882433597597</v>
+        <v>-0.0847904736559095</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.05748596741152587</v>
+        <v>-0.07067643589905147</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.08571816072910454</v>
+        <v>-0.03315452830631724</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.1087602545934374</v>
+        <v>-0.1320806896664829</v>
       </c>
       <c r="BW14" t="n">
         <v>-0</v>
@@ -8055,10 +8055,10 @@
         <v>-0</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.09823411546148268</v>
+        <v>0.01472617522666507</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.2721891536069246</v>
+        <v>0.1310315472618229</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
@@ -8073,34 +8073,34 @@
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.07861483346028969</v>
+        <v>0.07407259607048379</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.05135513785207683</v>
+        <v>-0.04641885809491544</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0.2043129677907541</v>
+        <v>-0.07448456780050969</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
         <v>-0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.0514453918371791</v>
+        <v>0.05723610841634751</v>
       </c>
       <c r="CO14" t="n">
         <v>0</v>
@@ -8109,16 +8109,16 @@
         <v>0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.2593940484279468</v>
+        <v>-0.1099368965743418</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.03063390755282392</v>
+        <v>-0.01557560789063341</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU14" t="n">
         <v>0</v>
@@ -8127,61 +8127,61 @@
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.05908299028522825</v>
+        <v>0.06964424193540865</v>
       </c>
       <c r="CX14" t="n">
         <v>-0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.03623008007098741</v>
+        <v>-0.05935632571522591</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0.2062664070779253</v>
+        <v>-0.09917386776563673</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.04141135020070766</v>
+        <v>0.0971357913697226</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.0905901842875516</v>
+        <v>0.04183536614768178</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.07402491111291939</v>
+        <v>-0.0502169546412565</v>
       </c>
       <c r="DK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL14" t="n">
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.02820244492951384</v>
+        <v>-0.03307262464890974</v>
       </c>
       <c r="DP14" t="n">
         <v>-0</v>
@@ -8190,13 +8190,13 @@
         <v>-0</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.1019373597298211</v>
+        <v>0.05958142805787685</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.08235226720640965</v>
+        <v>-0.08903085906318707</v>
       </c>
       <c r="DT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
@@ -8208,19 +8208,19 @@
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.08015565888284445</v>
+        <v>0.09012448454440626</v>
       </c>
       <c r="DY14" t="n">
         <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.05666788756798959</v>
+        <v>-0.01181821311779927</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.1225630172305461</v>
+        <v>0.002936186132100436</v>
       </c>
       <c r="EC14" t="n">
         <v>0</v>
@@ -8229,106 +8229,106 @@
         <v>-0</v>
       </c>
       <c r="EE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF14" t="n">
         <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.05561377214507678</v>
+        <v>0.05353277958034066</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.02504866241739046</v>
+        <v>-0.05198449150644427</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0.1211240756501744</v>
+        <v>0.01481817184556554</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO14" t="n">
         <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.01483852739103692</v>
+        <v>0.05900344545523646</v>
       </c>
       <c r="EQ14" t="n">
         <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.0317136911513799</v>
+        <v>-0.04857452648898018</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0.01109326151239741</v>
+        <v>0.04591305952067022</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
         <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
         <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0369122329486032</v>
+        <v>0.08804228160475704</v>
       </c>
       <c r="EZ14" t="n">
         <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.0647371640167072</v>
+        <v>-0.02829515694872746</v>
       </c>
       <c r="FC14" t="n">
-        <v>-0.1767849880194736</v>
+        <v>-0.08948781536527958</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.04842237741095196</v>
+        <v>-0.04496413381023746</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
         <v>0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.01737408666937787</v>
+        <v>0.01908697535428941</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0.1552452505490127</v>
+        <v>-0.1170274361714624</v>
       </c>
       <c r="FM14" t="n">
         <v>-0</v>
@@ -8343,55 +8343,55 @@
         <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.005672900845261564</v>
+        <v>-0.00247690984737604</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
         <v>0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.008225056864448643</v>
+        <v>0.009605553181029439</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0.2052803311436839</v>
+        <v>0.09771176450418144</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX14" t="n">
         <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.06256832481173993</v>
+        <v>0.05717110816535274</v>
       </c>
       <c r="GA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.00233280559055606</v>
+        <v>-0.07661384210471374</v>
       </c>
       <c r="GE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF14" t="n">
         <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.666877792282639</v>
+        <v>0.9154176255340356</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,25 +8408,25 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01734619152356717</v>
+        <v>-0.2952771180719096</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.832647884736646</v>
+        <v>-0.8210146960521149</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
         <v>-0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5830538301467535</v>
+        <v>1.161822300127267</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,13 +8435,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03681076055061933</v>
+        <v>-0.9796835448708368</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6807683665932025</v>
+        <v>-0.9466126626393371</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>-0</v>
@@ -8450,10 +8450,10 @@
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.05347593031280914</v>
+        <v>0.2769772541037757</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8462,43 +8462,43 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.05489386199670537</v>
+        <v>-0.1634675324324047</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1131082735367728</v>
+        <v>-0.1530207755476072</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1221656106063273</v>
+        <v>0.2007406169185788</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.05399033860117941</v>
+        <v>-0.4556709296773129</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.06211675020189908</v>
+        <v>-0.1809809179378997</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0</v>
@@ -8507,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.05753555440308916</v>
+        <v>0.357332246623919</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
@@ -8516,13 +8516,13 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.06692468641435227</v>
+        <v>0.1105079278586931</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.1510550103319466</v>
+        <v>-0.1858024631792063</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,22 +8531,22 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4012210113325229</v>
+        <v>1.716530802866336</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.01306373595801226</v>
+        <v>-0.2711362897776961</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.5503145890794698</v>
+        <v>-0.6107013642164573</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -8555,13 +8555,13 @@
         <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.1735334416913395</v>
+        <v>-0.5819687448278155</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,10 +8570,10 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1067608278672856</v>
+        <v>-0.2689609360229874</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.1680232339083514</v>
+        <v>0.02049538622569079</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
@@ -8585,10 +8585,10 @@
         <v>-0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1556789339865939</v>
+        <v>0.1356244800788722</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
@@ -8597,40 +8597,40 @@
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.0146194061496221</v>
+        <v>0.1856584314732913</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0.05649260644983728</v>
+        <v>0.138081535516047</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
         <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2012630801908264</v>
+        <v>0.6717759998778456</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.0133257623008405</v>
+        <v>-0.2066270931128476</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.2780819243863177</v>
+        <v>-0.3640407200538752</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
         <v>-0</v>
@@ -8639,25 +8639,25 @@
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1223278527839813</v>
+        <v>-0.3235804982403826</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.005254409864869247</v>
+        <v>0.1642646099514525</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.1166734183213457</v>
+        <v>0.2099296872523417</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
@@ -8669,88 +8669,88 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.03203105746107171</v>
+        <v>-0.3656273692701761</v>
       </c>
       <c r="CO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.05774787397121428</v>
+        <v>0.3987913114132937</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.03359273767830079</v>
+        <v>0.1828538613029201</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
         <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.1011671876862124</v>
+        <v>-0.2866392965304727</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.02000480567697621</v>
+        <v>0.1642145868638853</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.1152215963757141</v>
+        <v>0.2822667615579754</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.1182314721727722</v>
+        <v>-0.2345592387079171</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
         <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0926421827238085</v>
+        <v>-0.3778626267774362</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.2106009833430011</v>
+        <v>0.2633023963166696</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
       </c>
       <c r="DL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.0650262641083721</v>
+        <v>0.09170580695657705</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
@@ -8759,79 +8759,79 @@
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01764735801618293</v>
+        <v>-0.1085135878109885</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09823997440730246</v>
+        <v>0.1877288249857243</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW15" t="n">
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.06208792487795206</v>
+        <v>-0.2975882033812618</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.05390000122820674</v>
+        <v>0.06958224986686548</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.1122000894311024</v>
+        <v>0.05441078486052926</v>
       </c>
       <c r="EC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.07026254395707772</v>
+        <v>-0.2004448273991978</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.03001384433022367</v>
+        <v>0.116022166178487</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.003749114743894364</v>
+        <v>-0.06518256046486244</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.04986972815706415</v>
+        <v>0.1983197487913107</v>
       </c>
       <c r="EQ15" t="n">
         <v>0</v>
@@ -8840,52 +8840,52 @@
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.04334645757282828</v>
+        <v>0.006200669851622103</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.05738573424440058</v>
+        <v>0.1785873061320501</v>
       </c>
       <c r="EU15" t="n">
         <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.1014138461645648</v>
+        <v>-0.3596955428639713</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.003386850940089787</v>
+        <v>0.09376687730621741</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.1088160320204838</v>
+        <v>0.2474087535909296</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.03453703976720383</v>
+        <v>-0.2007603589976811</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
@@ -8894,13 +8894,13 @@
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.03300842387970353</v>
+        <v>0.1265693348354134</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.1145182047420687</v>
+        <v>0.2646402280863294</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
         <v>0</v>
@@ -8912,19 +8912,19 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.0108966448489025</v>
+        <v>-0.1418217932065887</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.140430721209814</v>
+        <v>0.3975011866316001</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.1777522919048</v>
+        <v>-0.1703091867510553</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
@@ -8936,28 +8936,28 @@
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.04727438391383657</v>
+        <v>-0.01817749321557701</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.1039745515608788</v>
+        <v>0.07345275855659406</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>0</v>
@@ -8968,43 +8968,43 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3815591499003186</v>
+        <v>0.4461305712729974</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.04031820273067106</v>
+        <v>-0.1986620095522671</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1372862478133693</v>
+        <v>0.01181099634678071</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2435578500743352</v>
+        <v>0.4504705668989015</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.05174992223808234</v>
+        <v>-0.2690757329511134</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1157256571373122</v>
+        <v>-0.05319611388135223</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -9022,79 +9022,79 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.07085902158143438</v>
+        <v>0.07390396228625766</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.008882736592941261</v>
+        <v>-0.05825248555488427</v>
       </c>
       <c r="W16" t="n">
-        <v>0.04507021695259513</v>
+        <v>-0.01881476674452279</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.03407889997012099</v>
+        <v>0.009764027054499792</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.01273148610218255</v>
+        <v>-0.1502414545083642</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.01709980036681078</v>
+        <v>0.01144924257941493</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.001000983457054746</v>
+        <v>0.1088075246020502</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.04944051060127548</v>
+        <v>-0.06124552354016068</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.06932520049972174</v>
+        <v>0.09845015623371056</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
@@ -9103,25 +9103,25 @@
         <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2604126056039317</v>
+        <v>0.3047941533022991</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.05322798495097165</v>
+        <v>-0.07950848856990177</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.03162657731251656</v>
+        <v>-0.1318852038334846</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,25 +9130,25 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.02234415291684705</v>
+        <v>-0.005861337058742435</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.08897726345042128</v>
+        <v>-0.1051546304923273</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1265616280370284</v>
+        <v>-0.01611512253239625</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -9157,16 +9157,16 @@
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.09905711066796725</v>
+        <v>-0.003149744362867394</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.03361156205481524</v>
+        <v>0.004925217054181013</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1060862496961958</v>
+        <v>0.04210998662296928</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
@@ -9181,100 +9181,100 @@
         <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1318263427938593</v>
+        <v>0.2154682670337422</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.02683384308305879</v>
+        <v>-0.04338195055731589</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.02556803323831543</v>
+        <v>-0.02500136902072409</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.06842268743063633</v>
+        <v>-0.1247219495712694</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0.007370990906041244</v>
+        <v>0.09834728440461291</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.00174222058358812</v>
+        <v>-0.0133724601163946</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.001543126283749217</v>
+        <v>-0.1024331777876969</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.03297968427095651</v>
+        <v>0.1382949193181361</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.08622357198756364</v>
+        <v>0.03873126281042349</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT16" t="n">
         <v>-0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.04864314265208998</v>
+        <v>-0.1213552857570784</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.008126848658402783</v>
+        <v>0.1107492481003431</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.005188538148519289</v>
+        <v>-0.005546055592276195</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
@@ -9292,16 +9292,16 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.06851578783708522</v>
+        <v>-0.07312814168706695</v>
       </c>
       <c r="DG16" t="n">
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.05839160801293795</v>
+        <v>0.04822040261229554</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.03828391387821059</v>
+        <v>-0.0445480601830337</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9316,22 +9316,22 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.03758317981213508</v>
+        <v>-0.07336638472573317</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.06052461104964519</v>
+        <v>-0.0612509612091002</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.03833446326475788</v>
+        <v>-0.002849066979302629</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9346,52 +9346,52 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.05442476172407507</v>
+        <v>-0.1008983247691735</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.01820028796003152</v>
+        <v>0.04576855740015798</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.03268597666039669</v>
+        <v>0.0363914610438491</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
         <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.07101584452534648</v>
+        <v>-0.1048014177554082</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.003949653990835863</v>
+        <v>0.09924609789597735</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.06245577001313934</v>
+        <v>0.007229874952478376</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>-0</v>
@@ -9400,22 +9400,22 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.001217797657538762</v>
+        <v>0.02896946540527011</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.003610769204830474</v>
+        <v>0.04087595639908014</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.03441009876344996</v>
+        <v>0.00506994986952817</v>
       </c>
       <c r="ET16" t="n">
         <v>0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
@@ -9427,16 +9427,16 @@
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.05125216831541067</v>
+        <v>-0.1394693185391009</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0.004213261535751177</v>
+        <v>0.1195182165512341</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.009170404765505871</v>
+        <v>-0.01989906592662548</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
@@ -9448,49 +9448,49 @@
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.007312756378878193</v>
+        <v>-0.03327846927940543</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.02002750736334317</v>
+        <v>0.06910947984829478</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.05103089366939924</v>
+        <v>-0.1128259980178284</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
       </c>
       <c r="FM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.04224751003496299</v>
+        <v>-0.1750365850483613</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.06318730042829301</v>
+        <v>0.06186546127645406</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.01581456421084561</v>
+        <v>0.1411185388781749</v>
       </c>
       <c r="FU16" t="n">
         <v>-0</v>
@@ -9499,34 +9499,34 @@
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.01914538716685472</v>
+        <v>-0.1072203876966592</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.04661998742545439</v>
+        <v>0.06450276871826796</v>
       </c>
       <c r="GC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
         <v>-0</v>
